--- a/MAJEntreesCDA/ig/StructureDefinition-fr-cda-batterie-examens-de-biologie-medicale.xlsx
+++ b/MAJEntreesCDA/ig/StructureDefinition-fr-cda-batterie-examens-de-biologie-medicale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T09:38:07+00:00</t>
+    <t>2026-04-20T13:30:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4305,7 +4305,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>157</v>
       </c>
@@ -4324,7 +4324,7 @@
         <v>75</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>74</v>
@@ -4709,7 +4709,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>166</v>
       </c>
@@ -4724,13 +4724,13 @@
         <v>62</v>
       </c>
       <c r="F30" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>74</v>
@@ -4812,7 +4812,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>169</v>
       </c>
@@ -4827,13 +4827,13 @@
         <v>170</v>
       </c>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>74</v>
@@ -5121,7 +5121,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>181</v>
       </c>
@@ -5136,13 +5136,13 @@
         <v>182</v>
       </c>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>74</v>
